--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 17:17</t>
+          <t>22/05/2026 18:35</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 17:17</t>
+          <t>22/05/2026 18:35</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 17:17</t>
+          <t>22/05/2026 18:35</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:35</t>
+          <t>22/05/2026 18:37</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:35</t>
+          <t>22/05/2026 18:37</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:35</t>
+          <t>22/05/2026 18:37</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:37</t>
+          <t>22/05/2026 18:40</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:37</t>
+          <t>22/05/2026 18:40</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:37</t>
+          <t>22/05/2026 18:40</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:40</t>
+          <t>22/05/2026 18:47</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:40</t>
+          <t>22/05/2026 18:47</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:40</t>
+          <t>22/05/2026 18:47</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:47</t>
+          <t>22/05/2026 18:50</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:47</t>
+          <t>22/05/2026 18:50</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:47</t>
+          <t>22/05/2026 18:50</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:50</t>
+          <t>22/05/2026 18:52</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:50</t>
+          <t>22/05/2026 18:52</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:50</t>
+          <t>22/05/2026 18:52</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:52</t>
+          <t>22/05/2026 18:55</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:52</t>
+          <t>22/05/2026 18:55</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:52</t>
+          <t>22/05/2026 18:55</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:55</t>
+          <t>22/05/2026 18:57</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:55</t>
+          <t>22/05/2026 18:57</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:55</t>
+          <t>22/05/2026 18:57</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:57</t>
+          <t>22/05/2026 19:00</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>22/05/2026 18:57</t>
+          <t>22/05/2026 19:00</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>22/05/2026 18:57</t>
+          <t>22/05/2026 19:00</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 09:54</t>
+          <t>23/05/2026 10:08</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 09:54</t>
+          <t>23/05/2026 10:08</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:08</t>
+          <t>23/05/2026 10:10</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:08</t>
+          <t>23/05/2026 10:10</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:10</t>
+          <t>23/05/2026 10:13</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:10</t>
+          <t>23/05/2026 10:13</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:13</t>
+          <t>23/05/2026 10:14</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:13</t>
+          <t>23/05/2026 10:14</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -530,12 +530,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Certificados Excelencias Académicas 1 pages-to-jpg-0001</t>
+          <t>Excelencia academica-B26-1</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Certificados Excelencias Académicas 1_pages-to-jpg-0001.png</t>
+          <t>Excelencia academica-B26-1.png</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:14</t>
+          <t>23/05/2026 10:20</t>
         </is>
       </c>
     </row>
@@ -565,12 +565,12 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Certificados Excelencias Académicas 1 pages-to-jpg-0002</t>
+          <t>Excelencia academica-B26-2</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Certificados Excelencias Académicas 1_pages-to-jpg-0002.png</t>
+          <t>Excelencia academica-B26-2.png</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -590,24 +590,708 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-3</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-3.png</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>A260031.pdf</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>A260031</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260031.pdf</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-4</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-4.png</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>A260042.pdf</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>A260042</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260042.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-5</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-5.png</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>A260053.pdf</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>A260053</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260053.pdf</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-6</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Excelencia academica-B26-6.png</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>A260064.pdf</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>A260064</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260064.pdf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-1</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-1.png</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>A260075.pdf</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>A260075</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260075.pdf</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-10</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-10.png</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>A260086.pdf</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>A260086</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260086.pdf</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-11</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-11.png</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>A260097.pdf</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>A260097</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260097.pdf</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-12</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-12.png</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>A260109.pdf</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>A260109</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260109.pdf</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-2</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-2.png</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>A260110.pdf</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>A260110</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260110.pdf</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-3</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-3.png</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>A260121.pdf</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>A260121</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260121.pdf</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-4</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-4.png</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>A260132.pdf</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>A260132</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260132.pdf</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-5</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-5.png</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>A260143.pdf</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>A260143</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260143.pdf</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-6.png</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>A260154.pdf</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>A260154</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260154.pdf</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-7</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-7.png</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>A260165.pdf</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>A260165</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260165.pdf</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-8</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Hackaton Final-8.png</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>A260176.pdf</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>A260176</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260176.pdf</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-9</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Hackaton Final-9.png</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>A260187.pdf</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>A260187</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260187.pdf</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Mejores docentes-1</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Mejores docentes-1.png</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>A260198.pdf</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>A260198</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260198.pdf</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Mejores docentes-2</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Mejores docentes-2.png</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>A260200.pdf</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>A260200</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260200.pdf</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Mejores docentes-3</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Mejores docentes-3.png</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>A260211.pdf</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>A260211</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260211.pdf</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>2</v>
+      <c r="B23" s="8" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:20</t>
+          <t>23/05/2026 10:29</t>
         </is>
       </c>
     </row>

--- a/registro_certificados.xlsx
+++ b/registro_certificados.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
+          <t>23/05/2026 10:33</t>
         </is>
       </c>
     </row>
@@ -1255,18 +1255,613 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>23/05/2026 10:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-1.png</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>A260222.pdf</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>A260222</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260222.pdf</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-10</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-10.png</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>A260233.pdf</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>A260233</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260233.pdf</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-11</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-11.png</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>A260244.pdf</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>A260244</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260244.pdf</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-12</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-12.png</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>A260255.pdf</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>A260255</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260255.pdf</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-13</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-13.png</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>A260266.pdf</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>A260266</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260266.pdf</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-14</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-14.png</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>A260277.pdf</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>A260277</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260277.pdf</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-15</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-15.png</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>A260288.pdf</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>A260288</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260288.pdf</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-16</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-16.png</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>A260299.pdf</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>A260299</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260299.pdf</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-17</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-17.png</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>A260301.pdf</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>A260301</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260301.pdf</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-2</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-2.png</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>A260312.pdf</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>A260312</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260312.pdf</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-3</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-3.png</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>A260323.pdf</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>A260323</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260323.pdf</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-4</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-4.png</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>A260334.pdf</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>A260334</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260334.pdf</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-5</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-5.png</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>A260345.pdf</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>A260345</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260345.pdf</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-6</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-6.png</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>A260356.pdf</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>A260356</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260356.pdf</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-7</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-7.png</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>A260367.pdf</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>A260367</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260367.pdf</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-8</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Mejores promedios-8.png</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>A260378.pdf</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>A260378</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260378.pdf</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-9</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Mejores promedios-9.png</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>A260389.pdf</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>A260389</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>https://fing-uti.github.io/certificados-semana-ing-2026a/A260389.pdf</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>23/05/2026 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>21</v>
+      <c r="B40" s="8" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1292,6 +1887,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
